--- a/STM/test_data.xlsx
+++ b/STM/test_data.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
